--- a/data/trans_camb/P57_AF_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P57_AF_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 5,57</t>
+          <t>-7,93; 5,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 15,87</t>
+          <t>2,11; 15,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,71; -0,65</t>
+          <t>-13,6; -0,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 15,53</t>
+          <t>0,18; 15,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,4; 25,59</t>
+          <t>10,6; 25,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,06; -2,03</t>
+          <t>-15,75; -1,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 7,72</t>
+          <t>-2,39; 8,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,46; 17,42</t>
+          <t>7,6; 17,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,26; -4,07</t>
+          <t>-13,04; -3,51</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 10,02</t>
+          <t>-13,1; 9,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 28,4</t>
+          <t>3,53; 27,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,27; -1,21</t>
+          <t>-22,52; -1,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 31,44</t>
+          <t>0,18; 31,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,73; 53,43</t>
+          <t>18,85; 53,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,44; -4,16</t>
+          <t>-26,85; -3,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 14,17</t>
+          <t>-4,0; 15,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,17; 32,07</t>
+          <t>12,7; 32,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-22,29; -7,37</t>
+          <t>-21,83; -6,45</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 14,43</t>
+          <t>0,53; 14,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,21; 23,01</t>
+          <t>8,99; 23,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 9,32</t>
+          <t>-4,21; 10,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 14,36</t>
+          <t>-0,46; 14,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 18,05</t>
+          <t>4,28; 17,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 4,17</t>
+          <t>-9,36; 3,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 12,13</t>
+          <t>1,17; 11,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,32; 18,34</t>
+          <t>8,72; 19,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 4,98</t>
+          <t>-5,57; 4,5</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 28,49</t>
+          <t>0,96; 29,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,42; 46,21</t>
+          <t>15,61; 47,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 18,48</t>
+          <t>-7,29; 21,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 25,76</t>
+          <t>-0,76; 25,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,01; 32,43</t>
+          <t>6,75; 31,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 7,59</t>
+          <t>-14,99; 7,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 22,38</t>
+          <t>1,99; 22,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,9; 33,86</t>
+          <t>15,05; 35,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 9,47</t>
+          <t>-9,55; 8,38</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 1,32</t>
+          <t>-9,3; 2,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,16; 16,46</t>
+          <t>5,05; 16,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-51,83; -5,54</t>
+          <t>-52,62; -4,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 10,35</t>
+          <t>-8,16; 10,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 23,2</t>
+          <t>3,65; 23,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 2,06</t>
+          <t>-16,72; 2,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 1,89</t>
+          <t>-7,6; 2,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,92; 16,21</t>
+          <t>6,57; 16,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-49,0; -5,94</t>
+          <t>-48,51; -5,71</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 2,12</t>
+          <t>-13,53; 3,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,65; 26,33</t>
+          <t>7,43; 26,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-80,11; -8,58</t>
+          <t>-78,38; -7,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 17,56</t>
+          <t>-11,83; 18,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,16; 39,56</t>
+          <t>5,41; 41,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,85; 3,35</t>
+          <t>-23,88; 4,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 3,03</t>
+          <t>-11,52; 3,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,24; 26,3</t>
+          <t>9,48; 26,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-74,15; -9,34</t>
+          <t>-74,14; -8,58</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 4,28</t>
+          <t>-3,68; 4,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,42; 15,16</t>
+          <t>7,34; 15,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,13; -0,25</t>
+          <t>-9,48; -0,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 10,34</t>
+          <t>0,29; 10,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,38; 14,14</t>
+          <t>4,98; 14,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 18,79</t>
+          <t>-10,33; 17,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 5,73</t>
+          <t>-0,69; 5,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,66; 13,56</t>
+          <t>7,66; 13,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 10,14</t>
+          <t>-7,27; 10,39</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 7,0</t>
+          <t>-5,46; 7,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,16; 24,64</t>
+          <t>11,03; 24,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-13,88; -0,38</t>
+          <t>-14,57; -0,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,81; 16,74</t>
+          <t>0,5; 16,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,47; 22,52</t>
+          <t>7,12; 23,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 29,54</t>
+          <t>-15,54; 28,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 9,26</t>
+          <t>-1,11; 8,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,74; 21,64</t>
+          <t>11,62; 21,92</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 16,16</t>
+          <t>-11,23; 15,85</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 11,29</t>
+          <t>-2,36; 11,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,06; 21,22</t>
+          <t>8,97; 21,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 7,12</t>
+          <t>-7,07; 7,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 8,51</t>
+          <t>-1,4; 8,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,38; 19,54</t>
+          <t>9,79; 19,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-26,16; -1,38</t>
+          <t>-22,76; -1,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 8,37</t>
+          <t>-0,36; 8,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,76; 18,35</t>
+          <t>10,59; 18,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-16,56; -0,21</t>
+          <t>-17,6; -0,2</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 19,25</t>
+          <t>-3,6; 19,73</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>13,52; 36,52</t>
+          <t>13,58; 37,15</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 11,93</t>
+          <t>-10,56; 12,57</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 13,19</t>
+          <t>-2,0; 13,81</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>13,62; 30,96</t>
+          <t>13,95; 30,97</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-38,11; -2,35</t>
+          <t>-33,13; -2,7</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 13,43</t>
+          <t>-0,52; 13,29</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>16,07; 29,45</t>
+          <t>15,34; 29,35</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-25,19; -0,4</t>
+          <t>-26,12; -0,46</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 11,62</t>
+          <t>-4,18; 11,97</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>14,62; 30,46</t>
+          <t>14,64; 30,11</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-22,57; 0,4</t>
+          <t>-23,13; 0,52</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,97; 8,8</t>
+          <t>0,81; 9,25</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>14,29; 21,75</t>
+          <t>14,55; 22,16</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 4,7</t>
+          <t>-4,09; 4,84</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,23; 8,43</t>
+          <t>1,25; 8,77</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>15,53; 22,13</t>
+          <t>15,35; 22,5</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 1,59</t>
+          <t>-7,38; 1,53</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 26,97</t>
+          <t>-8,23; 26,84</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>27,79; 70,14</t>
+          <t>28,94; 69,71</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-45,43; 1,26</t>
+          <t>-46,56; 1,07</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1,48; 15,38</t>
+          <t>1,33; 16,21</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>23,71; 38,35</t>
+          <t>24,27; 39,78</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 8,2</t>
+          <t>-6,73; 8,66</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,15; 15,31</t>
+          <t>2,27; 16,28</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>26,41; 40,53</t>
+          <t>26,19; 41,22</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 2,9</t>
+          <t>-12,53; 3,0</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 4,03</t>
+          <t>-1,42; 3,52</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>10,94; 15,56</t>
+          <t>10,85; 15,46</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-21,87; -3,76</t>
+          <t>-21,94; -3,67</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,08; 7,82</t>
+          <t>3,07; 7,71</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>12,48; 16,98</t>
+          <t>12,47; 16,94</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 5,75</t>
+          <t>-7,35; 4,45</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,14</t>
+          <t>1,82; 5,09</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>12,35; 15,63</t>
+          <t>12,43; 15,53</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-11,73; -1,79</t>
+          <t>-11,78; -1,6</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 6,75</t>
+          <t>-2,26; 5,91</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>17,66; 26,19</t>
+          <t>17,58; 26,04</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-35,11; -6,23</t>
+          <t>-36,26; -6,09</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4,96; 13,12</t>
+          <t>4,95; 12,84</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>19,82; 28,39</t>
+          <t>19,87; 28,35</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 9,74</t>
+          <t>-11,96; 7,31</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,94; 8,63</t>
+          <t>3,02; 8,5</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>19,92; 26,03</t>
+          <t>20,02; 25,74</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-19,17; -2,91</t>
+          <t>-19,17; -2,62</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57_AF_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P57_AF_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-7,7</t>
+          <t>-7,16</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-8,45</t>
+          <t>-7,74</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-8,49</t>
+          <t>-7,86</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 5,31</t>
+          <t>-7,61; 6,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 15,15</t>
+          <t>2,23; 15,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,6; -0,93</t>
+          <t>-13,57; -1,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 15,75</t>
+          <t>-0,54; 15,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,6; 25,57</t>
+          <t>9,36; 24,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,75; -1,56</t>
+          <t>-14,75; -0,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 8,4</t>
+          <t>-2,6; 7,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,6; 17,18</t>
+          <t>7,48; 17,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,04; -3,51</t>
+          <t>-12,62; -3,02</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-13,03%</t>
+          <t>-12,1%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-15,8%</t>
+          <t>-14,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-14,91%</t>
+          <t>-13,81%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 9,24</t>
+          <t>-12,31; 10,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 27,19</t>
+          <t>3,76; 27,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,52; -1,92</t>
+          <t>-21,93; -2,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 31,22</t>
+          <t>-0,27; 31,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,85; 53,21</t>
+          <t>16,94; 50,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,85; -3,06</t>
+          <t>-25,29; -1,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 15,75</t>
+          <t>-4,38; 14,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,7; 32,18</t>
+          <t>12,63; 31,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-21,83; -6,45</t>
+          <t>-21,26; -5,7</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,27</t>
+          <t>3,97</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,07</t>
+          <t>-3,3</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>0,37</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 14,59</t>
+          <t>-0,66; 14,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,99; 23,75</t>
+          <t>9,18; 22,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 10,1</t>
+          <t>-2,85; 10,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 14,2</t>
+          <t>-0,69; 14,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 17,81</t>
+          <t>3,87; 17,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 3,87</t>
+          <t>-9,64; 2,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 11,91</t>
+          <t>1,34; 11,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,72; 19,05</t>
+          <t>8,07; 17,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 4,5</t>
+          <t>-4,61; 5,27</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-5,18%</t>
+          <t>-5,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-0,77%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 29,59</t>
+          <t>-1,23; 28,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,61; 47,78</t>
+          <t>16,31; 46,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 21,3</t>
+          <t>-4,97; 21,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 25,33</t>
+          <t>-1,08; 26,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,75; 31,85</t>
+          <t>6,02; 32,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 7,2</t>
+          <t>-15,33; 4,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 22,27</t>
+          <t>2,38; 22,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,05; 35,73</t>
+          <t>13,71; 33,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 8,38</t>
+          <t>-7,75; 9,8</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-28,75</t>
+          <t>-7,8</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-7,05</t>
+          <t>-7,76</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-24,4</t>
+          <t>-7,84</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 2,12</t>
+          <t>-9,96; 1,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,05; 16,57</t>
+          <t>5,46; 16,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-52,62; -4,97</t>
+          <t>-13,77; -1,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 10,56</t>
+          <t>-9,32; 10,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,65; 23,83</t>
+          <t>3,06; 24,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 2,32</t>
+          <t>-17,37; 1,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 2,24</t>
+          <t>-7,56; 2,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,57; 16,62</t>
+          <t>6,78; 16,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-48,51; -5,71</t>
+          <t>-13,45; -2,38</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-43,97%</t>
+          <t>-11,93%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-10,96%</t>
+          <t>-12,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-37,45%</t>
+          <t>-12,03%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 3,36</t>
+          <t>-14,65; 2,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,43; 26,7</t>
+          <t>8,02; 27,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-78,38; -7,99</t>
+          <t>-20,43; -2,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 18,23</t>
+          <t>-13,4; 17,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,41; 41,12</t>
+          <t>4,91; 42,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,88; 4,02</t>
+          <t>-25,59; 2,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 3,58</t>
+          <t>-11,24; 3,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,48; 26,47</t>
+          <t>10,17; 26,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-74,14; -8,58</t>
+          <t>-19,96; -3,79</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-4,69</t>
+          <t>-4,66</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>-7,41</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,03</t>
+          <t>-5,76</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 4,58</t>
+          <t>-3,79; 4,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,34; 15,03</t>
+          <t>7,8; 15,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,48; -0,41</t>
+          <t>-8,71; -0,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 10,16</t>
+          <t>0,29; 10,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,98; 14,76</t>
+          <t>4,97; 14,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 17,82</t>
+          <t>-12,56; -2,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 5,34</t>
+          <t>-0,82; 5,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,66; 13,66</t>
+          <t>7,44; 13,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 10,39</t>
+          <t>-9,05; -2,48</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-7,34%</t>
+          <t>-7,3%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>-11,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-3,15%</t>
+          <t>-8,95%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 7,4</t>
+          <t>-5,75; 7,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,03; 24,3</t>
+          <t>11,8; 25,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-14,57; -0,7</t>
+          <t>-13,25; -0,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 16,5</t>
+          <t>0,33; 17,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,12; 23,77</t>
+          <t>7,32; 23,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 28,44</t>
+          <t>-18,19; -4,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 8,5</t>
+          <t>-1,23; 8,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,62; 21,92</t>
+          <t>11,37; 21,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 15,85</t>
+          <t>-13,69; -3,86</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>1,65</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-9,5</t>
+          <t>-0,7</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-5,98</t>
+          <t>0,17</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 11,6</t>
+          <t>-1,68; 11,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,97; 21,2</t>
+          <t>8,9; 20,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 7,27</t>
+          <t>-5,39; 9,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 8,74</t>
+          <t>-1,76; 8,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,79; 19,35</t>
+          <t>9,22; 19,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-22,76; -1,67</t>
+          <t>-5,28; 3,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 8,39</t>
+          <t>-0,25; 8,22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,59; 18,42</t>
+          <t>10,43; 18,48</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-17,6; -0,2</t>
+          <t>-4,13; 4,17</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-14,28%</t>
+          <t>-1,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-9,19%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 19,73</t>
+          <t>-2,61; 18,98</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>13,58; 37,15</t>
+          <t>12,9; 35,91</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 12,57</t>
+          <t>-7,94; 15,74</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 13,81</t>
+          <t>-2,49; 14,17</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>13,95; 30,97</t>
+          <t>12,83; 30,94</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-33,13; -2,7</t>
+          <t>-7,58; 6,09</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 13,29</t>
+          <t>-0,36; 13,31</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>15,34; 29,35</t>
+          <t>15,32; 29,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-26,12; -0,46</t>
+          <t>-6,08; 6,7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-12,15</t>
+          <t>-8,83</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>1,29</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-2,96</t>
+          <t>-1,21</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 11,97</t>
+          <t>-3,62; 12,29</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>14,64; 30,11</t>
+          <t>14,48; 29,46</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 0,52</t>
+          <t>-19,91; 1,84</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,81; 9,25</t>
+          <t>1,46; 9,42</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>14,55; 22,16</t>
+          <t>14,79; 21,87</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 4,84</t>
+          <t>-3,26; 5,49</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,25; 8,77</t>
+          <t>1,13; 8,57</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>15,35; 22,5</t>
+          <t>15,26; 22,26</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 1,53</t>
+          <t>-5,86; 2,94</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-25,44%</t>
+          <t>-18,48%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-5,24%</t>
+          <t>-2,15%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 26,84</t>
+          <t>-7,33; 27,88</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>28,94; 69,71</t>
+          <t>27,42; 69,2</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-46,56; 1,07</t>
+          <t>-39,46; 4,12</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1,33; 16,21</t>
+          <t>2,37; 16,39</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>24,27; 39,78</t>
+          <t>24,46; 38,78</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 8,66</t>
+          <t>-5,4; 9,64</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,27; 16,28</t>
+          <t>1,99; 15,6</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>26,19; 41,22</t>
+          <t>26,21; 40,55</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 3,0</t>
+          <t>-10,12; 5,34</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-8,76</t>
+          <t>-3,64</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-2,95</t>
+          <t>-3,02</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-5,77</t>
+          <t>-3,32</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 3,52</t>
+          <t>-0,95; 3,66</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>10,85; 15,46</t>
+          <t>10,75; 15,54</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-21,94; -3,67</t>
+          <t>-6,29; -1,21</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,07; 7,71</t>
+          <t>3,26; 7,88</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>12,47; 16,94</t>
+          <t>12,53; 16,83</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 4,45</t>
+          <t>-5,22; -0,93</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,09</t>
+          <t>1,92; 5,14</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>12,43; 15,53</t>
+          <t>12,39; 15,62</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-11,78; -1,6</t>
+          <t>-5,05; -1,62</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-14,43%</t>
+          <t>-5,99%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-4,81%</t>
+          <t>-4,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-9,46%</t>
+          <t>-5,44%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 5,91</t>
+          <t>-1,51; 6,14</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>17,58; 26,04</t>
+          <t>17,29; 26,06</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-36,26; -6,09</t>
+          <t>-10,25; -1,98</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4,95; 12,84</t>
+          <t>5,15; 13,26</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>19,87; 28,35</t>
+          <t>19,99; 28,03</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 7,31</t>
+          <t>-8,37; -1,48</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,02; 8,5</t>
+          <t>3,11; 8,57</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>20,02; 25,74</t>
+          <t>20,12; 26,08</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-19,17; -2,62</t>
+          <t>-8,19; -2,67</t>
         </is>
       </c>
     </row>
